--- a/data/nzd0480/nzd0480.xlsx
+++ b/data/nzd0480/nzd0480.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D610"/>
+  <dimension ref="A1:D612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11412,6 +11412,42 @@
       <c r="D610" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>336.89</v>
+      </c>
+      <c r="C611" t="n">
+        <v>342.13</v>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:28+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>337.02</v>
+      </c>
+      <c r="C612" t="n">
+        <v>341.87</v>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B750"/>
+  <dimension ref="A1:B752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18929,6 +18965,26 @@
       </c>
       <c r="B750" t="n">
         <v>0.67</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -19097,28 +19153,28 @@
         <v>0.0568</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1480333105984765</v>
+        <v>-0.1494134766848279</v>
       </c>
       <c r="J2" t="n">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="K2" t="n">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09817878536836433</v>
+        <v>0.1002545209163906</v>
       </c>
       <c r="M2" t="n">
-        <v>2.5606022337218</v>
+        <v>2.558511897316314</v>
       </c>
       <c r="N2" t="n">
-        <v>9.357930753418625</v>
+        <v>9.341599216809936</v>
       </c>
       <c r="O2" t="n">
-        <v>3.05907351226129</v>
+        <v>3.056402986651128</v>
       </c>
       <c r="P2" t="n">
-        <v>342.9458082425533</v>
+        <v>342.9623010659374</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -19179,28 +19235,28 @@
         <v>0.0603</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09786956681899099</v>
+        <v>-0.09867510121745811</v>
       </c>
       <c r="J3" t="n">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="K3" t="n">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0654142092690394</v>
+        <v>0.06676068636853782</v>
       </c>
       <c r="M3" t="n">
-        <v>1.971349085765256</v>
+        <v>1.969134381850248</v>
       </c>
       <c r="N3" t="n">
-        <v>6.362100731283364</v>
+        <v>6.346194443190021</v>
       </c>
       <c r="O3" t="n">
-        <v>2.52232050526561</v>
+        <v>2.519165425927806</v>
       </c>
       <c r="P3" t="n">
-        <v>345.8020293414801</v>
+        <v>345.8116560185798</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -19242,7 +19298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D610"/>
+  <dimension ref="A1:D612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32665,6 +32721,50 @@
         </is>
       </c>
     </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>-45.257791162413135,170.86286536223307</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>-45.25840762794977,170.86264922173788</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:28+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>-45.25779154567215,170.86286692711533</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>-45.258406861427794,170.86264609194177</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0480/nzd0480.xlsx
+++ b/data/nzd0480/nzd0480.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D612"/>
+  <dimension ref="A1:D613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11446,6 +11446,24 @@
         <v>341.87</v>
       </c>
       <c r="D612" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:20:39+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>337.31</v>
+      </c>
+      <c r="C613" t="n">
+        <v>341.57</v>
+      </c>
+      <c r="D613" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11462,7 +11480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B752"/>
+  <dimension ref="A1:B754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18985,6 +19003,26 @@
       </c>
       <c r="B752" t="n">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>
@@ -19153,28 +19191,28 @@
         <v>0.0568</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1494134766848279</v>
+        <v>-0.1499772063840011</v>
       </c>
       <c r="J2" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K2" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1002545209163906</v>
+        <v>0.1011698905744376</v>
       </c>
       <c r="M2" t="n">
-        <v>2.558511897316314</v>
+        <v>2.55690657607451</v>
       </c>
       <c r="N2" t="n">
-        <v>9.341599216809936</v>
+        <v>9.331131037236833</v>
       </c>
       <c r="O2" t="n">
-        <v>3.056402986651128</v>
+        <v>3.054690006733389</v>
       </c>
       <c r="P2" t="n">
-        <v>342.9623010659374</v>
+        <v>342.9690466655434</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -19235,28 +19273,28 @@
         <v>0.0603</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09867510121745811</v>
+        <v>-0.09921424098070657</v>
       </c>
       <c r="J3" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K3" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06676068636853782</v>
+        <v>0.06759380197619735</v>
       </c>
       <c r="M3" t="n">
-        <v>1.969134381850248</v>
+        <v>1.968740725125379</v>
       </c>
       <c r="N3" t="n">
-        <v>6.346194443190021</v>
+        <v>6.340211448407306</v>
       </c>
       <c r="O3" t="n">
-        <v>2.519165425927806</v>
+        <v>2.517977650497976</v>
       </c>
       <c r="P3" t="n">
-        <v>345.8116560185798</v>
+        <v>345.8181073745753</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -19298,7 +19336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D612"/>
+  <dimension ref="A1:D613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32765,6 +32803,28 @@
         </is>
       </c>
     </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:20:39+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>-45.25779240063442,170.8628704180066</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>-45.25840597697925,170.86264248063864</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0480/nzd0480.xlsx
+++ b/data/nzd0480/nzd0480.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D613"/>
+  <dimension ref="A1:D617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11466,6 +11466,78 @@
       <c r="D613" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>338.66</v>
+      </c>
+      <c r="C614" t="n">
+        <v>338.14</v>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>339.56</v>
+      </c>
+      <c r="C615" t="n">
+        <v>339.2</v>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="n">
+        <v>339.86</v>
+      </c>
+      <c r="C616" t="n">
+        <v>339.77</v>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>339.49</v>
+      </c>
+      <c r="C617" t="n">
+        <v>340.2</v>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B754"/>
+  <dimension ref="A1:B758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19023,6 +19095,46 @@
       </c>
       <c r="B754" t="n">
         <v>0.48</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -19191,28 +19303,28 @@
         <v>0.0568</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1499772063840011</v>
+        <v>-0.1494446312228342</v>
       </c>
       <c r="J2" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="K2" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1011698905744376</v>
+        <v>0.1016566487897123</v>
       </c>
       <c r="M2" t="n">
-        <v>2.55690657607451</v>
+        <v>2.544204086774398</v>
       </c>
       <c r="N2" t="n">
-        <v>9.331131037236833</v>
+        <v>9.272888518689992</v>
       </c>
       <c r="O2" t="n">
-        <v>3.054690006733389</v>
+        <v>3.045141789587144</v>
       </c>
       <c r="P2" t="n">
-        <v>342.9690466655434</v>
+        <v>342.9626103811436</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -19273,28 +19385,28 @@
         <v>0.0603</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09921424098070657</v>
+        <v>-0.1042919267632249</v>
       </c>
       <c r="J3" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="K3" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06759380197619735</v>
+        <v>0.07396881957084522</v>
       </c>
       <c r="M3" t="n">
-        <v>1.968740725125379</v>
+        <v>1.981914844040485</v>
       </c>
       <c r="N3" t="n">
-        <v>6.340211448407306</v>
+        <v>6.397733390761685</v>
       </c>
       <c r="O3" t="n">
-        <v>2.517977650497976</v>
+        <v>2.52937411047905</v>
       </c>
       <c r="P3" t="n">
-        <v>345.8181073745753</v>
+        <v>345.8794062530991</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -19336,7 +19448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D613"/>
+  <dimension ref="A1:D617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32825,6 +32937,94 @@
         </is>
       </c>
     </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>-45.257796380629934,170.86288666870877</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>-45.25839586477627,170.86260119141457</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>-45.25779903395899,170.86289750251152</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>-45.258398989831825,170.8626139513481</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>-45.25779991840179,170.86290111377934</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>-45.258400670285646,170.8626208128224</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>-45.25779882758899,170.86289665988238</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>-45.25840193799615,170.86262598902255</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0480/nzd0480.xlsx
+++ b/data/nzd0480/nzd0480.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D617"/>
+  <dimension ref="A1:D618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11536,6 +11536,24 @@
         <v>340.2</v>
       </c>
       <c r="D617" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>339.59</v>
+      </c>
+      <c r="C618" t="n">
+        <v>340.54</v>
+      </c>
+      <c r="D618" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11552,7 +11570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B758"/>
+  <dimension ref="A1:B759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19135,6 +19153,16 @@
       </c>
       <c r="B758" t="n">
         <v>-0.87</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>
@@ -19303,28 +19331,28 @@
         <v>0.0568</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1494446312228342</v>
+        <v>-0.149244053429774</v>
       </c>
       <c r="J2" t="n">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K2" t="n">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1016566487897123</v>
+        <v>0.1016970704751128</v>
       </c>
       <c r="M2" t="n">
-        <v>2.544204086774398</v>
+        <v>2.541131552202825</v>
       </c>
       <c r="N2" t="n">
-        <v>9.272888518689992</v>
+        <v>9.258451573436087</v>
       </c>
       <c r="O2" t="n">
-        <v>3.045141789587144</v>
+        <v>3.042770378033165</v>
       </c>
       <c r="P2" t="n">
-        <v>342.9626103811436</v>
+        <v>342.9601781941527</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -19385,28 +19413,28 @@
         <v>0.0603</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1042919267632249</v>
+        <v>-0.1051403281068062</v>
       </c>
       <c r="J3" t="n">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K3" t="n">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07396881957084522</v>
+        <v>0.07519315555478046</v>
       </c>
       <c r="M3" t="n">
-        <v>1.981914844040485</v>
+        <v>1.983008090373903</v>
       </c>
       <c r="N3" t="n">
-        <v>6.397733390761685</v>
+        <v>6.397956672511999</v>
       </c>
       <c r="O3" t="n">
-        <v>2.52937411047905</v>
+        <v>2.52941824784119</v>
       </c>
       <c r="P3" t="n">
-        <v>345.8794062530991</v>
+        <v>345.8896938860393</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -19448,7 +19476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D617"/>
+  <dimension ref="A1:D618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33025,6 +33053,28 @@
         </is>
       </c>
     </row>
+    <row r="618">
+      <c r="A618" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>-45.25779912240327,170.8628978636383</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>-45.25840294037173,170.86263008183215</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0480/nzd0480.xlsx
+++ b/data/nzd0480/nzd0480.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D618"/>
+  <dimension ref="A1:D624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11554,6 +11554,114 @@
         <v>340.54</v>
       </c>
       <c r="D618" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:13:44+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>339.06</v>
+      </c>
+      <c r="C619" t="n">
+        <v>340.37</v>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:19:53+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>338.4</v>
+      </c>
+      <c r="C620" t="n">
+        <v>339.96</v>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>338.86</v>
+      </c>
+      <c r="C621" t="n">
+        <v>340.96</v>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>338.28</v>
+      </c>
+      <c r="C622" t="n">
+        <v>341.14</v>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>338.55</v>
+      </c>
+      <c r="C623" t="n">
+        <v>342.51</v>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>340.02</v>
+      </c>
+      <c r="C624" t="n">
+        <v>344.14</v>
+      </c>
+      <c r="D624" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11570,7 +11678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B759"/>
+  <dimension ref="A1:B765"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19163,6 +19271,66 @@
       </c>
       <c r="B759" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B760" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B761" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B762" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B763" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B764" t="n">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B765" t="n">
+        <v>-0.84</v>
       </c>
     </row>
   </sheetData>
@@ -19331,28 +19499,28 @@
         <v>0.0568</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.149244053429774</v>
+        <v>-0.1494657713001816</v>
       </c>
       <c r="J2" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="K2" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1016970704751128</v>
+        <v>0.1036831247947669</v>
       </c>
       <c r="M2" t="n">
-        <v>2.541131552202825</v>
+        <v>2.521306377435457</v>
       </c>
       <c r="N2" t="n">
-        <v>9.258451573436087</v>
+        <v>9.172689398262625</v>
       </c>
       <c r="O2" t="n">
-        <v>3.042770378033165</v>
+        <v>3.028644812166429</v>
       </c>
       <c r="P2" t="n">
-        <v>342.9601781941527</v>
+        <v>342.962869378826</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -19413,28 +19581,28 @@
         <v>0.0603</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1051403281068062</v>
+        <v>-0.1081817169022662</v>
       </c>
       <c r="J3" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="K3" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07519315555478046</v>
+        <v>0.08015750701261248</v>
       </c>
       <c r="M3" t="n">
-        <v>1.983008090373903</v>
+        <v>1.982677452055045</v>
       </c>
       <c r="N3" t="n">
-        <v>6.397956672511999</v>
+        <v>6.378766474494804</v>
       </c>
       <c r="O3" t="n">
-        <v>2.52941824784119</v>
+        <v>2.525621997547298</v>
       </c>
       <c r="P3" t="n">
-        <v>345.8896938860393</v>
+        <v>345.9266322893902</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -19476,7 +19644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D618"/>
+  <dimension ref="A1:D624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33075,6 +33243,138 @@
         </is>
       </c>
     </row>
+    <row r="619">
+      <c r="A619" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:13:44+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>-45.25779755988741,170.86289148373208</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>-45.25840243918396,170.86262803542732</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:19:53+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>-45.25779561411245,170.86288353894372</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>-45.25840123043682,170.86262309998057</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>-45.257796970258696,170.8628890762204</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>-45.25840417860021,170.862635137656</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>-45.25779526033512,170.8628820944368</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>-45.25840470926948,170.8626373044377</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>-45.25779605633408,170.8628853445774</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>-45.25840874825097,170.86265379605547</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>-45.25780039010456,170.86290303978888</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>-45.25841355375145,170.86267341747245</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0480/nzd0480.xlsx
+++ b/data/nzd0480/nzd0480.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D624"/>
+  <dimension ref="A1:D627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11662,6 +11662,60 @@
         <v>344.14</v>
       </c>
       <c r="D624" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:19:39+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>339.48</v>
+      </c>
+      <c r="C625" t="n">
+        <v>344.53</v>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>339.21</v>
+      </c>
+      <c r="C626" t="n">
+        <v>345.07</v>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>337.84</v>
+      </c>
+      <c r="C627" t="n">
+        <v>344.69</v>
+      </c>
+      <c r="D627" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11678,7 +11732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B765"/>
+  <dimension ref="A1:B769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19331,6 +19385,46 @@
       </c>
       <c r="B765" t="n">
         <v>-0.84</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B766" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B767" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B768" t="n">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B769" t="n">
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>
@@ -19499,28 +19593,28 @@
         <v>0.0568</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1494657713001816</v>
+        <v>-0.1495779402274239</v>
       </c>
       <c r="J2" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="K2" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1036831247947669</v>
+        <v>0.1046753965977661</v>
       </c>
       <c r="M2" t="n">
-        <v>2.521306377435457</v>
+        <v>2.512198929222538</v>
       </c>
       <c r="N2" t="n">
-        <v>9.172689398262625</v>
+        <v>9.131251329685931</v>
       </c>
       <c r="O2" t="n">
-        <v>3.028644812166429</v>
+        <v>3.021796043694202</v>
       </c>
       <c r="P2" t="n">
-        <v>342.962869378826</v>
+        <v>342.9642425923761</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -19581,28 +19675,28 @@
         <v>0.0603</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1081817169022662</v>
+        <v>-0.1065022328042386</v>
       </c>
       <c r="J3" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="K3" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08015750701261248</v>
+        <v>0.07839385713298397</v>
       </c>
       <c r="M3" t="n">
-        <v>1.982677452055045</v>
+        <v>1.981232397048273</v>
       </c>
       <c r="N3" t="n">
-        <v>6.378766474494804</v>
+        <v>6.362679520168805</v>
       </c>
       <c r="O3" t="n">
-        <v>2.525621997547298</v>
+        <v>2.522435236070256</v>
       </c>
       <c r="P3" t="n">
-        <v>345.9266322893902</v>
+        <v>345.9061303433258</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -19644,7 +19738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D624"/>
+  <dimension ref="A1:D627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33375,6 +33469,72 @@
         </is>
       </c>
     </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:19:39+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>-45.25779879810755,170.86289653950678</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>-45.25841470353329,170.86267811216783</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>-45.257798002108906,170.86289328936587</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>-45.25841629553858,170.86268461251555</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>-45.25779396315145,170.8628767979116</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>-45.258415175238596,170.86268003819671</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
